--- a/sources/kazuya_step6b.xlsx
+++ b/sources/kazuya_step6b.xlsx
@@ -738,6 +738,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
@@ -775,6 +780,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
@@ -817,6 +827,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
@@ -869,6 +884,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
@@ -916,6 +936,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
@@ -961,6 +986,11 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>cc572ca8-7e2b-4695-be36-969d95d53b5c</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -4704,6 +4734,11 @@
           <t>hh"hh"mm"Lhmm</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr">
         <is>
           <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
@@ -4736,6 +4771,11 @@
           <t>hh'hh"mm"LL"m!</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr">
         <is>
           <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
@@ -4766,6 +4806,11 @@
       <c r="K83" t="inlineStr">
         <is>
           <t>hh"mm"sm"L"m!</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>ca41b863-8414-4a05-af5c-d5d050d26435</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">

--- a/sources/kazuya_step6b.xlsx
+++ b/sources/kazuya_step6b.xlsx
@@ -760,6 +760,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -805,6 +810,11 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>– 2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
